--- a/upload/situacao.xlsx
+++ b/upload/situacao.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2065"/>
+  <dimension ref="A1:G2068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68501,7 +68501,11 @@
           <t>DC-9507997/2026</t>
         </is>
       </c>
-      <c r="B2032" t="inlineStr"/>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C2032" t="inlineStr">
         <is>
           <t>A Iniciar</t>
@@ -68523,23 +68527,23 @@
     <row r="2033">
       <c r="A2033" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B2033" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C2033" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2033" t="inlineStr"/>
       <c r="E2033" t="inlineStr">
         <is>
-          <t>2026-03-18 00:00:00</t>
+          <t>2026-05-14 00:00:00</t>
         </is>
       </c>
       <c r="F2033" t="inlineStr">
@@ -68547,21 +68551,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2033" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+      <c r="G2033" t="inlineStr"/>
     </row>
     <row r="2034">
       <c r="A2034" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B2034" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C2034" t="inlineStr">
@@ -68589,12 +68589,12 @@
     <row r="2035">
       <c r="A2035" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B2035" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C2035" t="inlineStr">
@@ -68622,12 +68622,12 @@
     <row r="2036">
       <c r="A2036" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B2036" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C2036" t="inlineStr">
@@ -68638,7 +68638,7 @@
       <c r="D2036" t="inlineStr"/>
       <c r="E2036" t="inlineStr">
         <is>
-          <t>2026-04-06 00:00:00</t>
+          <t>2026-03-18 00:00:00</t>
         </is>
       </c>
       <c r="F2036" t="inlineStr">
@@ -68648,7 +68648,7 @@
       </c>
       <c r="G2036" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
@@ -68688,10 +68688,14 @@
     <row r="2038">
       <c r="A2038" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
-        </is>
-      </c>
-      <c r="B2038" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B2038" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C2038" t="inlineStr">
         <is>
           <t>Andamento</t>
@@ -68700,7 +68704,7 @@
       <c r="D2038" t="inlineStr"/>
       <c r="E2038" t="inlineStr">
         <is>
-          <t>2026-06-01 00:00:00</t>
+          <t>2026-04-06 00:00:00</t>
         </is>
       </c>
       <c r="F2038" t="inlineStr">
@@ -68708,28 +68712,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2038" t="inlineStr"/>
+      <c r="G2038" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="2039">
       <c r="A2039" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B2039" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C2039" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2039" t="inlineStr"/>
       <c r="E2039" t="inlineStr">
         <is>
-          <t>2026-03-17 00:00:00</t>
+          <t>2026-04-06 00:00:00</t>
         </is>
       </c>
       <c r="F2039" t="inlineStr">
@@ -68739,19 +68747,19 @@
       </c>
       <c r="G2039" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="2040">
       <c r="A2040" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B2040" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C2040" t="inlineStr">
@@ -68762,7 +68770,7 @@
       <c r="D2040" t="inlineStr"/>
       <c r="E2040" t="inlineStr">
         <is>
-          <t>2026-04-01 00:00:00</t>
+          <t>2026-04-06 00:00:00</t>
         </is>
       </c>
       <c r="F2040" t="inlineStr">
@@ -68772,30 +68780,26 @@
       </c>
       <c r="G2040" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="2041">
       <c r="A2041" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
-        </is>
-      </c>
-      <c r="B2041" t="inlineStr">
-        <is>
-          <t>9453556</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B2041" t="inlineStr"/>
       <c r="C2041" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2041" t="inlineStr"/>
       <c r="E2041" t="inlineStr">
         <is>
-          <t>2026-03-20 00:00:00</t>
+          <t>2026-06-01 00:00:00</t>
         </is>
       </c>
       <c r="F2041" t="inlineStr">
@@ -68803,32 +68807,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2041" t="inlineStr">
-        <is>
-          <t>2301520 000041/2025</t>
-        </is>
-      </c>
+      <c r="G2041" t="inlineStr"/>
     </row>
     <row r="2042">
       <c r="A2042" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B2042" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C2042" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2042" t="inlineStr"/>
       <c r="E2042" t="inlineStr">
         <is>
-          <t>2026-04-09 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="F2042" t="inlineStr">
@@ -68838,19 +68838,19 @@
       </c>
       <c r="G2042" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="2043">
       <c r="A2043" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B2043" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C2043" t="inlineStr">
@@ -68861,7 +68861,7 @@
       <c r="D2043" t="inlineStr"/>
       <c r="E2043" t="inlineStr">
         <is>
-          <t>2026-04-08 00:00:00</t>
+          <t>2026-04-01 00:00:00</t>
         </is>
       </c>
       <c r="F2043" t="inlineStr">
@@ -68871,30 +68871,30 @@
       </c>
       <c r="G2043" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="2044">
       <c r="A2044" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B2044" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C2044" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2044" t="inlineStr"/>
       <c r="E2044" t="inlineStr">
         <is>
-          <t>2026-04-10 00:00:00</t>
+          <t>2026-03-20 00:00:00</t>
         </is>
       </c>
       <c r="F2044" t="inlineStr">
@@ -68904,19 +68904,19 @@
       </c>
       <c r="G2044" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="2045">
       <c r="A2045" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B2045" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C2045" t="inlineStr">
@@ -68927,7 +68927,7 @@
       <c r="D2045" t="inlineStr"/>
       <c r="E2045" t="inlineStr">
         <is>
-          <t>2026-04-08 00:00:00</t>
+          <t>2026-04-09 00:00:00</t>
         </is>
       </c>
       <c r="F2045" t="inlineStr">
@@ -68944,10 +68944,14 @@
     <row r="2046">
       <c r="A2046" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B2046" t="inlineStr"/>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B2046" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
       <c r="C2046" t="inlineStr">
         <is>
           <t>Andamento</t>
@@ -68956,7 +68960,7 @@
       <c r="D2046" t="inlineStr"/>
       <c r="E2046" t="inlineStr">
         <is>
-          <t>2026-05-08 00:00:00</t>
+          <t>2026-04-08 00:00:00</t>
         </is>
       </c>
       <c r="F2046" t="inlineStr">
@@ -68964,28 +68968,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2046" t="inlineStr"/>
+      <c r="G2046" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="2047">
       <c r="A2047" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B2047" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C2047" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2047" t="inlineStr"/>
       <c r="E2047" t="inlineStr">
         <is>
-          <t>2026-03-24 00:00:00</t>
+          <t>2026-04-10 00:00:00</t>
         </is>
       </c>
       <c r="F2047" t="inlineStr">
@@ -68995,19 +69003,19 @@
       </c>
       <c r="G2047" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="2048">
       <c r="A2048" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B2048" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C2048" t="inlineStr">
@@ -69018,7 +69026,7 @@
       <c r="D2048" t="inlineStr"/>
       <c r="E2048" t="inlineStr">
         <is>
-          <t>2026-03-29 00:00:00</t>
+          <t>2026-04-08 00:00:00</t>
         </is>
       </c>
       <c r="F2048" t="inlineStr">
@@ -69028,21 +69036,17 @@
       </c>
       <c r="G2048" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="2049">
       <c r="A2049" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
-        </is>
-      </c>
-      <c r="B2049" t="inlineStr">
-        <is>
-          <t>9424449</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B2049" t="inlineStr"/>
       <c r="C2049" t="inlineStr">
         <is>
           <t>Andamento</t>
@@ -69051,7 +69055,7 @@
       <c r="D2049" t="inlineStr"/>
       <c r="E2049" t="inlineStr">
         <is>
-          <t>2026-05-02 00:00:00</t>
+          <t>2026-05-08 00:00:00</t>
         </is>
       </c>
       <c r="F2049" t="inlineStr">
@@ -69059,32 +69063,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2049" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
+      <c r="G2049" t="inlineStr"/>
     </row>
     <row r="2050">
       <c r="A2050" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B2050" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C2050" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2050" t="inlineStr"/>
       <c r="E2050" t="inlineStr">
         <is>
-          <t>2026-05-01 00:00:00</t>
+          <t>2026-03-24 00:00:00</t>
         </is>
       </c>
       <c r="F2050" t="inlineStr">
@@ -69094,19 +69094,19 @@
       </c>
       <c r="G2050" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="2051">
       <c r="A2051" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B2051" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C2051" t="inlineStr">
@@ -69117,7 +69117,7 @@
       <c r="D2051" t="inlineStr"/>
       <c r="E2051" t="inlineStr">
         <is>
-          <t>2026-04-13 00:00:00</t>
+          <t>2026-03-29 00:00:00</t>
         </is>
       </c>
       <c r="F2051" t="inlineStr">
@@ -69127,30 +69127,30 @@
       </c>
       <c r="G2051" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="2052">
       <c r="A2052" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B2052" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C2052" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2052" t="inlineStr"/>
       <c r="E2052" t="inlineStr">
         <is>
-          <t>2026-05-06 00:00:00</t>
+          <t>2026-05-02 00:00:00</t>
         </is>
       </c>
       <c r="F2052" t="inlineStr">
@@ -69160,19 +69160,19 @@
       </c>
       <c r="G2052" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="2053">
       <c r="A2053" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B2053" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C2053" t="inlineStr">
@@ -69183,7 +69183,7 @@
       <c r="D2053" t="inlineStr"/>
       <c r="E2053" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-05-01 00:00:00</t>
         </is>
       </c>
       <c r="F2053" t="inlineStr">
@@ -69193,30 +69193,30 @@
       </c>
       <c r="G2053" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="2054">
       <c r="A2054" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B2054" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C2054" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2054" t="inlineStr"/>
       <c r="E2054" t="inlineStr">
         <is>
-          <t>2026-05-07 00:00:00</t>
+          <t>2026-04-13 00:00:00</t>
         </is>
       </c>
       <c r="F2054" t="inlineStr">
@@ -69226,30 +69226,30 @@
       </c>
       <c r="G2054" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="2055">
       <c r="A2055" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B2055" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C2055" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2055" t="inlineStr"/>
       <c r="E2055" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-05-06 00:00:00</t>
         </is>
       </c>
       <c r="F2055" t="inlineStr">
@@ -69259,30 +69259,30 @@
       </c>
       <c r="G2055" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="2056">
       <c r="A2056" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B2056" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C2056" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2056" t="inlineStr"/>
       <c r="E2056" t="inlineStr">
         <is>
-          <t>2026-04-23 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
       <c r="F2056" t="inlineStr">
@@ -69292,30 +69292,30 @@
       </c>
       <c r="G2056" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="2057">
       <c r="A2057" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B2057" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C2057" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2057" t="inlineStr"/>
       <c r="E2057" t="inlineStr">
         <is>
-          <t>2026-03-04 00:00:00</t>
+          <t>2026-05-07 00:00:00</t>
         </is>
       </c>
       <c r="F2057" t="inlineStr">
@@ -69325,30 +69325,30 @@
       </c>
       <c r="G2057" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="2058">
       <c r="A2058" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B2058" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C2058" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="D2058" t="inlineStr"/>
       <c r="E2058" t="inlineStr">
         <is>
-          <t>2026-02-13 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
       <c r="F2058" t="inlineStr">
@@ -69358,30 +69358,30 @@
       </c>
       <c r="G2058" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="2059">
       <c r="A2059" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B2059" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C2059" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2059" t="inlineStr"/>
       <c r="E2059" t="inlineStr">
         <is>
-          <t>2026-04-11 00:00:00</t>
+          <t>2026-04-23 00:00:00</t>
         </is>
       </c>
       <c r="F2059" t="inlineStr">
@@ -69391,19 +69391,19 @@
       </c>
       <c r="G2059" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="2060">
       <c r="A2060" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B2060" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C2060" t="inlineStr">
@@ -69414,7 +69414,7 @@
       <c r="D2060" t="inlineStr"/>
       <c r="E2060" t="inlineStr">
         <is>
-          <t>2026-04-28 00:00:00</t>
+          <t>2026-03-04 00:00:00</t>
         </is>
       </c>
       <c r="F2060" t="inlineStr">
@@ -69424,19 +69424,19 @@
       </c>
       <c r="G2060" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="2061">
       <c r="A2061" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B2061" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C2061" t="inlineStr">
@@ -69447,7 +69447,7 @@
       <c r="D2061" t="inlineStr"/>
       <c r="E2061" t="inlineStr">
         <is>
-          <t>2026-04-16 00:00:00</t>
+          <t>2026-02-13 00:00:00</t>
         </is>
       </c>
       <c r="F2061" t="inlineStr">
@@ -69457,19 +69457,19 @@
       </c>
       <c r="G2061" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="2062">
       <c r="A2062" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B2062" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C2062" t="inlineStr">
@@ -69480,7 +69480,7 @@
       <c r="D2062" t="inlineStr"/>
       <c r="E2062" t="inlineStr">
         <is>
-          <t>2026-04-24 00:00:00</t>
+          <t>2026-04-11 00:00:00</t>
         </is>
       </c>
       <c r="F2062" t="inlineStr">
@@ -69490,19 +69490,19 @@
       </c>
       <c r="G2062" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="2063">
       <c r="A2063" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B2063" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C2063" t="inlineStr">
@@ -69513,7 +69513,7 @@
       <c r="D2063" t="inlineStr"/>
       <c r="E2063" t="inlineStr">
         <is>
-          <t>2026-04-26 00:00:00</t>
+          <t>2026-04-28 00:00:00</t>
         </is>
       </c>
       <c r="F2063" t="inlineStr">
@@ -69523,30 +69523,30 @@
       </c>
       <c r="G2063" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="2064">
       <c r="A2064" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B2064" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C2064" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="D2064" t="inlineStr"/>
       <c r="E2064" t="inlineStr">
         <is>
-          <t>2026-05-15 00:00:00</t>
+          <t>2026-04-16 00:00:00</t>
         </is>
       </c>
       <c r="F2064" t="inlineStr">
@@ -69556,19 +69556,19 @@
       </c>
       <c r="G2064" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="2065">
       <c r="A2065" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B2065" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C2065" t="inlineStr">
@@ -69579,15 +69579,114 @@
       <c r="D2065" t="inlineStr"/>
       <c r="E2065" t="inlineStr">
         <is>
+          <t>2026-04-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="F2065" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2065" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B2066" t="inlineStr">
+        <is>
+          <t>9424337</t>
+        </is>
+      </c>
+      <c r="C2066" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="D2066" t="inlineStr"/>
+      <c r="E2066" t="inlineStr">
+        <is>
+          <t>2026-04-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="F2066" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2066" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" t="inlineStr">
+        <is>
+          <t>DM-020/2024-A</t>
+        </is>
+      </c>
+      <c r="B2067" t="inlineStr">
+        <is>
+          <t>9427674</t>
+        </is>
+      </c>
+      <c r="C2067" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="D2067" t="inlineStr"/>
+      <c r="E2067" t="inlineStr">
+        <is>
+          <t>2026-05-15 00:00:00</t>
+        </is>
+      </c>
+      <c r="F2067" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2067" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" t="inlineStr">
+        <is>
+          <t>DM-022/2024-A</t>
+        </is>
+      </c>
+      <c r="B2068" t="inlineStr">
+        <is>
+          <t>9427765</t>
+        </is>
+      </c>
+      <c r="C2068" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="D2068" t="inlineStr"/>
+      <c r="E2068" t="inlineStr">
+        <is>
           <t>2026-05-16 00:00:00</t>
         </is>
       </c>
-      <c r="F2065" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G2065" t="inlineStr">
+      <c r="F2068" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2068" t="inlineStr">
         <is>
           <t>2301762 000051/2023</t>
         </is>

--- a/upload/situacao.xlsx
+++ b/upload/situacao.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27232,12 +27232,12 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>DP-003/2022</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>9344767</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -27248,7 +27248,7 @@
       <c r="D814" t="inlineStr"/>
       <c r="E814" t="inlineStr">
         <is>
-          <t>2026-03-04 00:00:00</t>
+          <t>2026-07-06 00:00:00</t>
         </is>
       </c>
       <c r="F814" t="inlineStr">
@@ -27258,19 +27258,19 @@
       </c>
       <c r="G814" t="inlineStr">
         <is>
-          <t>2301601 000001/2022</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DP-003/2022</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9344767</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -27281,7 +27281,7 @@
       <c r="D815" t="inlineStr"/>
       <c r="E815" t="inlineStr">
         <is>
-          <t>2026-04-10 00:00:00</t>
+          <t>2026-03-04 00:00:00</t>
         </is>
       </c>
       <c r="F815" t="inlineStr">
@@ -27291,19 +27291,19 @@
       </c>
       <c r="G815" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301601 000001/2022</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -27314,7 +27314,7 @@
       <c r="D816" t="inlineStr"/>
       <c r="E816" t="inlineStr">
         <is>
-          <t>2026-04-08 00:00:00</t>
+          <t>2026-04-10 00:00:00</t>
         </is>
       </c>
       <c r="F816" t="inlineStr">
@@ -27331,12 +27331,12 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -27364,12 +27364,12 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>9479677</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -27380,7 +27380,7 @@
       <c r="D818" t="inlineStr"/>
       <c r="E818" t="inlineStr">
         <is>
-          <t>2026-04-13 00:00:00</t>
+          <t>2026-04-08 00:00:00</t>
         </is>
       </c>
       <c r="F818" t="inlineStr">
@@ -27390,19 +27390,19 @@
       </c>
       <c r="G818" t="inlineStr">
         <is>
-          <t>2301520 000032/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9479677</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -27413,7 +27413,7 @@
       <c r="D819" t="inlineStr"/>
       <c r="E819" t="inlineStr">
         <is>
-          <t>2026-04-09 00:00:00</t>
+          <t>2026-04-13 00:00:00</t>
         </is>
       </c>
       <c r="F819" t="inlineStr">
@@ -27423,19 +27423,19 @@
       </c>
       <c r="G819" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000032/2025</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -27446,7 +27446,7 @@
       <c r="D820" t="inlineStr"/>
       <c r="E820" t="inlineStr">
         <is>
-          <t>2026-04-24 00:00:00</t>
+          <t>2026-04-09 00:00:00</t>
         </is>
       </c>
       <c r="F820" t="inlineStr">
@@ -27456,19 +27456,19 @@
       </c>
       <c r="G820" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -27479,7 +27479,7 @@
       <c r="D821" t="inlineStr"/>
       <c r="E821" t="inlineStr">
         <is>
-          <t>2026-04-11 00:00:00</t>
+          <t>2026-04-24 00:00:00</t>
         </is>
       </c>
       <c r="F821" t="inlineStr">
@@ -27489,19 +27489,19 @@
       </c>
       <c r="G821" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -27512,7 +27512,7 @@
       <c r="D822" t="inlineStr"/>
       <c r="E822" t="inlineStr">
         <is>
-          <t>2026-04-26 00:00:00</t>
+          <t>2026-04-11 00:00:00</t>
         </is>
       </c>
       <c r="F822" t="inlineStr">
@@ -27522,19 +27522,19 @@
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -27545,7 +27545,7 @@
       <c r="D823" t="inlineStr"/>
       <c r="E823" t="inlineStr">
         <is>
-          <t>2026-05-18 00:00:00</t>
+          <t>2026-04-26 00:00:00</t>
         </is>
       </c>
       <c r="F823" t="inlineStr">
@@ -27555,17 +27555,21 @@
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B824" t="inlineStr"/>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
       <c r="C824" t="inlineStr">
         <is>
           <t>Andamento</t>
@@ -27574,7 +27578,7 @@
       <c r="D824" t="inlineStr"/>
       <c r="E824" t="inlineStr">
         <is>
-          <t>2026-07-01 00:00:00</t>
+          <t>2026-05-18 00:00:00</t>
         </is>
       </c>
       <c r="F824" t="inlineStr">
@@ -27582,17 +27586,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G824" t="inlineStr"/>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -27603,7 +27611,7 @@
       <c r="D825" t="inlineStr"/>
       <c r="E825" t="inlineStr">
         <is>
-          <t>2026-03-18 00:00:00</t>
+          <t>2026-07-01 00:00:00</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
@@ -27613,19 +27621,19 @@
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -27653,12 +27661,12 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>DC-9445587/2024</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>9445587</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -27669,7 +27677,7 @@
       <c r="D827" t="inlineStr"/>
       <c r="E827" t="inlineStr">
         <is>
-          <t>2026-04-20 00:00:00</t>
+          <t>2026-03-18 00:00:00</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
@@ -27679,19 +27687,19 @@
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9445587/2024</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9445587</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -27702,7 +27710,7 @@
       <c r="D828" t="inlineStr"/>
       <c r="E828" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-04-20 00:00:00</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
@@ -27712,19 +27720,19 @@
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -27735,7 +27743,7 @@
       <c r="D829" t="inlineStr"/>
       <c r="E829" t="inlineStr">
         <is>
-          <t>2026-04-22 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
@@ -27745,19 +27753,19 @@
       </c>
       <c r="G829" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -27768,7 +27776,7 @@
       <c r="D830" t="inlineStr"/>
       <c r="E830" t="inlineStr">
         <is>
-          <t>2026-03-18 00:00:00</t>
+          <t>2026-04-22 00:00:00</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
@@ -27778,19 +27786,19 @@
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DP-026/2023</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>9393455</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -27801,7 +27809,7 @@
       <c r="D831" t="inlineStr"/>
       <c r="E831" t="inlineStr">
         <is>
-          <t>2026-03-04 00:00:00</t>
+          <t>2026-03-18 00:00:00</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -27811,19 +27819,19 @@
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>2301601 000015/2022</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DP-026/2023</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9393455</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -27844,19 +27852,19 @@
       </c>
       <c r="G832" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301601 000015/2022</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>DC-016/2023</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>9402062</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -27867,7 +27875,7 @@
       <c r="D833" t="inlineStr"/>
       <c r="E833" t="inlineStr">
         <is>
-          <t>2026-03-16 00:00:00</t>
+          <t>2026-03-04 00:00:00</t>
         </is>
       </c>
       <c r="F833" t="inlineStr">
@@ -27877,17 +27885,21 @@
       </c>
       <c r="G833" t="inlineStr">
         <is>
-          <t>1301606 000001/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B834" t="inlineStr"/>
+          <t>DC-016/2023</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>9402062</t>
+        </is>
+      </c>
       <c r="C834" t="inlineStr">
         <is>
           <t>Andamento</t>
@@ -27896,7 +27908,7 @@
       <c r="D834" t="inlineStr"/>
       <c r="E834" t="inlineStr">
         <is>
-          <t>2026-06-08 00:00:00</t>
+          <t>2026-03-16 00:00:00</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
@@ -27904,17 +27916,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G834" t="inlineStr"/>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>1301606 000001/2023</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
@@ -27925,7 +27941,7 @@
       <c r="D835" t="inlineStr"/>
       <c r="E835" t="inlineStr">
         <is>
-          <t>2026-04-06 00:00:00</t>
+          <t>2026-06-08 00:00:00</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
@@ -27935,19 +27951,19 @@
       </c>
       <c r="G835" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
@@ -27958,7 +27974,7 @@
       <c r="D836" t="inlineStr"/>
       <c r="E836" t="inlineStr">
         <is>
-          <t>2026-04-06 00:00:00</t>
+          <t>2026-07-01 00:00:00</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -27968,19 +27984,19 @@
       </c>
       <c r="G836" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C837" t="inlineStr">
@@ -27991,7 +28007,7 @@
       <c r="D837" t="inlineStr"/>
       <c r="E837" t="inlineStr">
         <is>
-          <t>2026-05-11 00:00:00</t>
+          <t>2026-04-06 00:00:00</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -28001,19 +28017,19 @@
       </c>
       <c r="G837" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C838" t="inlineStr">
@@ -28024,7 +28040,7 @@
       <c r="D838" t="inlineStr"/>
       <c r="E838" t="inlineStr">
         <is>
-          <t>2026-06-03 00:00:00</t>
+          <t>2026-05-11 00:00:00</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -28034,7 +28050,7 @@
       </c>
       <c r="G838" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
@@ -28074,12 +28090,12 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>DC-007/2024</t>
+          <t>DP-021/2023</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>9424592</t>
+          <t>9393558</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -28094,7 +28110,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>2026-02-20 00:00:00</t>
+          <t>2026-04-30 00:00:00</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -28104,19 +28120,19 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>2301520 000024/2023</t>
+          <t>2301601 000010/2022</t>
         </is>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>DP-025/2023</t>
+          <t>DC-007/2024</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>9394603</t>
+          <t>9424592</t>
         </is>
       </c>
       <c r="C841" t="inlineStr">
@@ -28131,7 +28147,7 @@
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>2026-03-20 00:00:00</t>
+          <t>2026-02-20 00:00:00</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -28141,19 +28157,19 @@
       </c>
       <c r="G841" t="inlineStr">
         <is>
-          <t>2301601 000014/2022</t>
+          <t>2301520 000024/2023</t>
         </is>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>PRC-24.014/2018</t>
+          <t>DP-025/2023</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>9292318</t>
+          <t>9394603</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -28168,7 +28184,7 @@
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>2026-03-05 00:00:00</t>
+          <t>2026-03-20 00:00:00</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -28178,19 +28194,19 @@
       </c>
       <c r="G842" t="inlineStr">
         <is>
-          <t>2301601 000005/2017</t>
+          <t>2301601 000014/2022</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>PRC-24.014/2018</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9417863</t>
+          <t>9292318</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -28200,12 +28216,12 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>Caso Fortuito ou Força Maior</t>
+          <t>Outros tipos de paralisação</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>2026-03-20 00:00:00</t>
+          <t>2026-03-05 00:00:00</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -28215,19 +28231,19 @@
       </c>
       <c r="G843" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301601 000005/2017</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DP-005/2023</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9383229</t>
+          <t>9417863</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -28237,12 +28253,12 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>Outros tipos de paralisação</t>
+          <t>Caso Fortuito ou Força Maior</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>2026-03-30 00:00:00</t>
+          <t>2026-03-20 00:00:00</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -28252,19 +28268,19 @@
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>2301601 000004/2022</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DP-026/2023</t>
+          <t>DP-005/2023</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9393455</t>
+          <t>9383229</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -28279,7 +28295,7 @@
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>2026-02-19 00:00:00</t>
+          <t>2026-03-30 00:00:00</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
@@ -28289,19 +28305,19 @@
       </c>
       <c r="G845" t="inlineStr">
         <is>
-          <t>2301601 000015/2022</t>
+          <t>2301601 000004/2022</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DP-020/2023</t>
+          <t>DP-026/2023</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9393315</t>
+          <t>9393455</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -28316,7 +28332,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>2026-02-10 00:00:00</t>
+          <t>2026-02-19 00:00:00</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
@@ -28326,19 +28342,19 @@
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>2301601 000009/2022</t>
+          <t>2301601 000015/2022</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DP-015/2023</t>
+          <t>DP-020/2023</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9386095</t>
+          <t>9393315</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -28353,7 +28369,7 @@
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>2024-03-18 00:00:00</t>
+          <t>2026-02-10 00:00:00</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
@@ -28363,19 +28379,19 @@
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>2301601 000009/2022</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DP-015/2023</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9447760</t>
+          <t>9386095</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -28385,12 +28401,12 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Caso Fortuito ou Força Maior</t>
+          <t>Outros tipos de paralisação</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>2025-05-01 00:00:00</t>
+          <t>2024-03-18 00:00:00</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
@@ -28400,19 +28416,19 @@
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DC-016/2023</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9402062</t>
+          <t>9447760</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -28427,7 +28443,7 @@
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>2025-10-01 00:00:00</t>
+          <t>2025-05-01 00:00:00</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -28437,19 +28453,19 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>1301606 000001/2023</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DP-009/2023</t>
+          <t>DC-016/2023</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9386090</t>
+          <t>9402062</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -28459,12 +28475,12 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>Outros tipos de paralisação</t>
+          <t>Caso Fortuito ou Força Maior</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>2023-11-01 00:00:00</t>
+          <t>2025-10-01 00:00:00</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
@@ -28474,19 +28490,19 @@
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>1301606 000001/2023</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DP-016/2023</t>
+          <t>DP-009/2023</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9386096</t>
+          <t>9386090</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -28518,12 +28534,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DP-024/2023</t>
+          <t>DP-016/2023</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9393398</t>
+          <t>9386096</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -28538,7 +28554,7 @@
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2023-11-01 00:00:00</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
@@ -28548,19 +28564,19 @@
       </c>
       <c r="G852" t="inlineStr">
         <is>
-          <t>2301601 000013/2022</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DC-004/2024</t>
+          <t>DP-024/2023</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9429715</t>
+          <t>9393398</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
@@ -28570,12 +28586,12 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>Caso Fortuito ou Força Maior</t>
+          <t>Outros tipos de paralisação</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>2025-08-01 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="F853" t="inlineStr">
@@ -28585,19 +28601,19 @@
       </c>
       <c r="G853" t="inlineStr">
         <is>
-          <t>2301520 000020/2023</t>
+          <t>2301601 000013/2022</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DM-018/2023</t>
+          <t>DC-004/2024</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9400070</t>
+          <t>9429715</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
@@ -28607,12 +28623,12 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>Outros tipos de paralisação</t>
+          <t>Caso Fortuito ou Força Maior</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>2024-02-07 00:00:00</t>
+          <t>2025-08-01 00:00:00</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
@@ -28622,19 +28638,19 @@
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>2301762 000026/2023</t>
+          <t>2301520 000020/2023</t>
         </is>
       </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DP-002/2022</t>
+          <t>DM-018/2023</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9370793</t>
+          <t>9400070</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -28649,7 +28665,7 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>2023-12-05 00:00:00</t>
+          <t>2024-02-07 00:00:00</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -28659,19 +28675,19 @@
       </c>
       <c r="G855" t="inlineStr">
         <is>
-          <t>2301601 000002/2022</t>
+          <t>2301762 000026/2023</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DC-9459023/2025</t>
+          <t>DP-002/2022</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9459023</t>
+          <t>9370793</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -28681,12 +28697,12 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Caso Fortuito ou Força Maior</t>
+          <t>Outros tipos de paralisação</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>2025-11-10 00:00:00</t>
+          <t>2023-12-05 00:00:00</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
@@ -28696,19 +28712,19 @@
       </c>
       <c r="G856" t="inlineStr">
         <is>
-          <t>2301520 000001/2025</t>
+          <t>2301601 000002/2022</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DC-028/2022</t>
+          <t>DC-9459023/2025</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9378009</t>
+          <t>9459023</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -28723,7 +28739,7 @@
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>2023-12-11 00:00:00</t>
+          <t>2025-11-10 00:00:00</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
@@ -28733,19 +28749,19 @@
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>2301520 000047/2022</t>
+          <t>2301520 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DM-040/2022</t>
+          <t>DC-028/2022</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9372557</t>
+          <t>9378009</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -28755,12 +28771,12 @@
       </c>
       <c r="D858" t="inlineStr">
         <is>
-          <t>Outros tipos de paralisação</t>
+          <t>Caso Fortuito ou Força Maior</t>
         </is>
       </c>
       <c r="E858" t="inlineStr">
         <is>
-          <t>2024-01-22 00:00:00</t>
+          <t>2023-12-11 00:00:00</t>
         </is>
       </c>
       <c r="F858" t="inlineStr">
@@ -28770,19 +28786,19 @@
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>2301762 000043/2022</t>
+          <t>2301520 000047/2022</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DP-017/2023</t>
+          <t>DM-040/2022</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9386097</t>
+          <t>9372557</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -28797,7 +28813,7 @@
       </c>
       <c r="E859" t="inlineStr">
         <is>
-          <t>2024-03-18 00:00:00</t>
+          <t>2024-01-22 00:00:00</t>
         </is>
       </c>
       <c r="F859" t="inlineStr">
@@ -28807,19 +28823,19 @@
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>2301762 000043/2022</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-008/2023</t>
+          <t>DP-017/2023</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9385831</t>
+          <t>9386097</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -28834,7 +28850,7 @@
       </c>
       <c r="E860" t="inlineStr">
         <is>
-          <t>2024-09-12 00:00:00</t>
+          <t>2024-03-18 00:00:00</t>
         </is>
       </c>
       <c r="F860" t="inlineStr">
@@ -28844,19 +28860,19 @@
       </c>
       <c r="G860" t="inlineStr">
         <is>
-          <t>2301520 000046/2022</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DC-005/2024</t>
+          <t>DC-008/2023</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9422256</t>
+          <t>9385831</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -28871,7 +28887,7 @@
       </c>
       <c r="E861" t="inlineStr">
         <is>
-          <t>2024-09-16 00:00:00</t>
+          <t>2024-09-12 00:00:00</t>
         </is>
       </c>
       <c r="F861" t="inlineStr">
@@ -28881,19 +28897,19 @@
       </c>
       <c r="G861" t="inlineStr">
         <is>
-          <t>2301520 000025/2023</t>
+          <t>2301520 000046/2022</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-002/2023</t>
+          <t>DC-005/2024</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9377832</t>
+          <t>9422256</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -28908,7 +28924,7 @@
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>2023-12-15 00:00:00</t>
+          <t>2024-09-16 00:00:00</t>
         </is>
       </c>
       <c r="F862" t="inlineStr">
@@ -28918,19 +28934,19 @@
       </c>
       <c r="G862" t="inlineStr">
         <is>
-          <t>2301762 000071/2022</t>
+          <t>2301520 000025/2023</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-015/2023</t>
+          <t>DM-002/2023</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9405799</t>
+          <t>9377832</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -28940,12 +28956,12 @@
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>Caso Fortuito ou Força Maior</t>
+          <t>Outros tipos de paralisação</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>2024-04-06 00:00:00</t>
+          <t>2023-12-15 00:00:00</t>
         </is>
       </c>
       <c r="F863" t="inlineStr">
@@ -28955,19 +28971,19 @@
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>2301520 000013/2023</t>
+          <t>2301762 000071/2022</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DP-020/2023</t>
+          <t>DC-015/2023</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9393315</t>
+          <t>9405799</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -28977,12 +28993,12 @@
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>Outros tipos de paralisação</t>
+          <t>Caso Fortuito ou Força Maior</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>2026-04-30 00:00:00</t>
+          <t>2024-04-06 00:00:00</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
@@ -28992,19 +29008,19 @@
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>2301601 000009/2022</t>
+          <t>2301520 000013/2023</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DP-022/2023</t>
+          <t>DP-020/2023</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>9393396</t>
+          <t>9393315</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -29019,7 +29035,7 @@
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>2026-05-25 00:00:00</t>
+          <t>2026-04-30 00:00:00</t>
         </is>
       </c>
       <c r="F865" t="inlineStr">
@@ -29029,19 +29045,19 @@
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>2301601 000011/2022</t>
+          <t>2301601 000009/2022</t>
         </is>
       </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DP-027/2023</t>
+          <t>DP-022/2023</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9393457</t>
+          <t>9393396</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -29056,7 +29072,7 @@
       </c>
       <c r="E866" t="inlineStr">
         <is>
-          <t>2026-04-17 00:00:00</t>
+          <t>2026-05-25 00:00:00</t>
         </is>
       </c>
       <c r="F866" t="inlineStr">
@@ -29066,19 +29082,19 @@
       </c>
       <c r="G866" t="inlineStr">
         <is>
-          <t>2301601 000016/2022</t>
+          <t>2301601 000011/2022</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DP-004/2023</t>
+          <t>DP-027/2023</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>9382502</t>
+          <t>9393457</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -29093,7 +29109,7 @@
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>2026-04-30 00:00:00</t>
+          <t>2026-04-17 00:00:00</t>
         </is>
       </c>
       <c r="F867" t="inlineStr">
@@ -29103,19 +29119,19 @@
       </c>
       <c r="G867" t="inlineStr">
         <is>
-          <t>2301601 000008/2022</t>
+          <t>2301601 000016/2022</t>
         </is>
       </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DP-021/2023</t>
+          <t>DP-004/2023</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9393558</t>
+          <t>9382502</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -29140,7 +29156,7 @@
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>2301601 000010/2022</t>
+          <t>2301601 000008/2022</t>
         </is>
       </c>
     </row>
@@ -51995,12 +52011,12 @@
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C1533" t="inlineStr">
@@ -52011,7 +52027,7 @@
       <c r="D1533" t="inlineStr"/>
       <c r="E1533" t="inlineStr">
         <is>
-          <t>2026-03-17 00:00:00</t>
+          <t>2026-05-07 00:00:00</t>
         </is>
       </c>
       <c r="F1533" t="inlineStr">
@@ -52021,19 +52037,19 @@
       </c>
       <c r="G1533" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C1534" t="inlineStr">
@@ -52044,7 +52060,7 @@
       <c r="D1534" t="inlineStr"/>
       <c r="E1534" t="inlineStr">
         <is>
-          <t>2026-02-13 00:00:00</t>
+          <t>2026-03-17 00:00:00</t>
         </is>
       </c>
       <c r="F1534" t="inlineStr">
@@ -52054,19 +52070,19 @@
       </c>
       <c r="G1534" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C1535" t="inlineStr">
@@ -52077,7 +52093,7 @@
       <c r="D1535" t="inlineStr"/>
       <c r="E1535" t="inlineStr">
         <is>
-          <t>2026-03-10 00:00:00</t>
+          <t>2026-02-13 00:00:00</t>
         </is>
       </c>
       <c r="F1535" t="inlineStr">
@@ -52087,17 +52103,21 @@
       </c>
       <c r="G1535" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B1536" t="inlineStr"/>
+          <t>DC-9495596/2026</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>9495596</t>
+        </is>
+      </c>
       <c r="C1536" t="inlineStr">
         <is>
           <t>A Iniciar</t>
@@ -52106,7 +52126,7 @@
       <c r="D1536" t="inlineStr"/>
       <c r="E1536" t="inlineStr">
         <is>
-          <t>2026-06-03 00:00:00</t>
+          <t>2026-03-10 00:00:00</t>
         </is>
       </c>
       <c r="F1536" t="inlineStr">
@@ -52114,15 +52134,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G1536" t="inlineStr"/>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>2301520 000030/2025</t>
+        </is>
+      </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B1537" t="inlineStr"/>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
       <c r="C1537" t="inlineStr">
         <is>
           <t>A Iniciar</t>
@@ -52131,7 +52159,7 @@
       <c r="D1537" t="inlineStr"/>
       <c r="E1537" t="inlineStr">
         <is>
-          <t>2026-06-24 00:00:00</t>
+          <t>2026-06-03 00:00:00</t>
         </is>
       </c>
       <c r="F1537" t="inlineStr">
@@ -52139,17 +52167,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G1537" t="inlineStr"/>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>DM-9445782/2024</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
         <is>
-          <t>9445782</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C1538" t="inlineStr">
@@ -52160,7 +52192,7 @@
       <c r="D1538" t="inlineStr"/>
       <c r="E1538" t="inlineStr">
         <is>
-          <t>2024-12-16 00:00:00</t>
+          <t>2026-07-02 00:00:00</t>
         </is>
       </c>
       <c r="F1538" t="inlineStr">
@@ -52170,19 +52202,19 @@
       </c>
       <c r="G1538" t="inlineStr">
         <is>
-          <t>2301762 000114/2024</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>DF/GTIC-9444079</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
         <is>
-          <t>9444079</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C1539" t="inlineStr">
@@ -52193,7 +52225,7 @@
       <c r="D1539" t="inlineStr"/>
       <c r="E1539" t="inlineStr">
         <is>
-          <t>2024-12-02 00:00:00</t>
+          <t>2026-06-24 00:00:00</t>
         </is>
       </c>
       <c r="F1539" t="inlineStr">
@@ -52203,19 +52235,19 @@
       </c>
       <c r="G1539" t="inlineStr">
         <is>
-          <t>2301403 000100/2024</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>DM-9445784/2024</t>
+          <t>DM-9445782/2024</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
         <is>
-          <t>9445784</t>
+          <t>9445782</t>
         </is>
       </c>
       <c r="C1540" t="inlineStr">
@@ -52236,19 +52268,19 @@
       </c>
       <c r="G1540" t="inlineStr">
         <is>
-          <t>2301762 000113/2024</t>
+          <t>2301762 000114/2024</t>
         </is>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>DM-030/2023-A</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
         <is>
-          <t>9408491</t>
+          <t>9444079</t>
         </is>
       </c>
       <c r="C1541" t="inlineStr">
@@ -52259,7 +52291,7 @@
       <c r="D1541" t="inlineStr"/>
       <c r="E1541" t="inlineStr">
         <is>
-          <t>2024-12-29 00:00:00</t>
+          <t>2024-12-02 00:00:00</t>
         </is>
       </c>
       <c r="F1541" t="inlineStr">
@@ -52269,19 +52301,19 @@
       </c>
       <c r="G1541" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301403 000100/2024</t>
         </is>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>DC-9445592/2024</t>
+          <t>DM-9445784/2024</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
         <is>
-          <t>9445592</t>
+          <t>9445784</t>
         </is>
       </c>
       <c r="C1542" t="inlineStr">
@@ -52292,7 +52324,7 @@
       <c r="D1542" t="inlineStr"/>
       <c r="E1542" t="inlineStr">
         <is>
-          <t>2024-12-04 00:00:00</t>
+          <t>2024-12-16 00:00:00</t>
         </is>
       </c>
       <c r="F1542" t="inlineStr">
@@ -52302,19 +52334,19 @@
       </c>
       <c r="G1542" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301762 000113/2024</t>
         </is>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>DER-30.014/2025</t>
+          <t>DM-030/2023-A</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>9408491</t>
         </is>
       </c>
       <c r="C1543" t="inlineStr">
@@ -52325,7 +52357,7 @@
       <c r="D1543" t="inlineStr"/>
       <c r="E1543" t="inlineStr">
         <is>
-          <t>2025-04-04 00:00:00</t>
+          <t>2024-12-29 00:00:00</t>
         </is>
       </c>
       <c r="F1543" t="inlineStr">
@@ -52335,19 +52367,19 @@
       </c>
       <c r="G1543" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>DM-015/2023</t>
+          <t>DC-9445592/2024</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
         <is>
-          <t>9394312</t>
+          <t>9445592</t>
         </is>
       </c>
       <c r="C1544" t="inlineStr">
@@ -52358,7 +52390,7 @@
       <c r="D1544" t="inlineStr"/>
       <c r="E1544" t="inlineStr">
         <is>
-          <t>2023-09-14 00:00:00</t>
+          <t>2024-12-04 00:00:00</t>
         </is>
       </c>
       <c r="F1544" t="inlineStr">
@@ -52368,19 +52400,19 @@
       </c>
       <c r="G1544" t="inlineStr">
         <is>
-          <t>2301762 000023/2023</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>DM-014/2023</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
         <is>
-          <t>9393682</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="C1545" t="inlineStr">
@@ -52391,7 +52423,7 @@
       <c r="D1545" t="inlineStr"/>
       <c r="E1545" t="inlineStr">
         <is>
-          <t>2023-09-14 00:00:00</t>
+          <t>2025-04-04 00:00:00</t>
         </is>
       </c>
       <c r="F1545" t="inlineStr">
@@ -52401,19 +52433,19 @@
       </c>
       <c r="G1545" t="inlineStr">
         <is>
-          <t>2301762 000024/2023</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>DM-023/2023</t>
+          <t>DM-015/2023</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
         <is>
-          <t>9408490</t>
+          <t>9394312</t>
         </is>
       </c>
       <c r="C1546" t="inlineStr">
@@ -52424,7 +52456,7 @@
       <c r="D1546" t="inlineStr"/>
       <c r="E1546" t="inlineStr">
         <is>
-          <t>2023-12-28 00:00:00</t>
+          <t>2023-09-14 00:00:00</t>
         </is>
       </c>
       <c r="F1546" t="inlineStr">
@@ -52434,19 +52466,19 @@
       </c>
       <c r="G1546" t="inlineStr">
         <is>
-          <t>2301762 000007/2023</t>
+          <t>2301762 000023/2023</t>
         </is>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>DM-005/2024</t>
+          <t>DM-014/2023</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9393682</t>
         </is>
       </c>
       <c r="C1547" t="inlineStr">
@@ -52457,7 +52489,7 @@
       <c r="D1547" t="inlineStr"/>
       <c r="E1547" t="inlineStr">
         <is>
-          <t>2024-03-14 00:00:00</t>
+          <t>2023-09-14 00:00:00</t>
         </is>
       </c>
       <c r="F1547" t="inlineStr">
@@ -52467,19 +52499,19 @@
       </c>
       <c r="G1547" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000024/2023</t>
         </is>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>DP-012/2023</t>
+          <t>DM-023/2023</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
         <is>
-          <t>9386092</t>
+          <t>9408490</t>
         </is>
       </c>
       <c r="C1548" t="inlineStr">
@@ -52490,7 +52522,7 @@
       <c r="D1548" t="inlineStr"/>
       <c r="E1548" t="inlineStr">
         <is>
-          <t>2023-04-27 00:00:00</t>
+          <t>2023-12-28 00:00:00</t>
         </is>
       </c>
       <c r="F1548" t="inlineStr">
@@ -52500,19 +52532,19 @@
       </c>
       <c r="G1548" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>2301762 000007/2023</t>
         </is>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>DC-017/2023</t>
+          <t>DM-005/2024</t>
         </is>
       </c>
       <c r="B1549" t="inlineStr">
         <is>
-          <t>9406230</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C1549" t="inlineStr">
@@ -52523,7 +52555,7 @@
       <c r="D1549" t="inlineStr"/>
       <c r="E1549" t="inlineStr">
         <is>
-          <t>2023-12-19 00:00:00</t>
+          <t>2024-03-14 00:00:00</t>
         </is>
       </c>
       <c r="F1549" t="inlineStr">
@@ -52533,19 +52565,19 @@
       </c>
       <c r="G1549" t="inlineStr">
         <is>
-          <t>2301520 000015/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>DM-021/2023</t>
+          <t>DP-012/2023</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
         <is>
-          <t>9406400</t>
+          <t>9386092</t>
         </is>
       </c>
       <c r="C1550" t="inlineStr">
@@ -52556,7 +52588,7 @@
       <c r="D1550" t="inlineStr"/>
       <c r="E1550" t="inlineStr">
         <is>
-          <t>2023-11-08 00:00:00</t>
+          <t>2023-04-27 00:00:00</t>
         </is>
       </c>
       <c r="F1550" t="inlineStr">
@@ -52566,19 +52598,19 @@
       </c>
       <c r="G1550" t="inlineStr">
         <is>
-          <t>2301762 000029/2023</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>DC-007/2024</t>
+          <t>DC-017/2023</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
         <is>
-          <t>9424592</t>
+          <t>9406230</t>
         </is>
       </c>
       <c r="C1551" t="inlineStr">
@@ -52589,7 +52621,7 @@
       <c r="D1551" t="inlineStr"/>
       <c r="E1551" t="inlineStr">
         <is>
-          <t>2024-04-15 00:00:00</t>
+          <t>2023-12-19 00:00:00</t>
         </is>
       </c>
       <c r="F1551" t="inlineStr">
@@ -52599,19 +52631,19 @@
       </c>
       <c r="G1551" t="inlineStr">
         <is>
-          <t>2301520 000024/2023</t>
+          <t>2301520 000015/2023</t>
         </is>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>DC-012/2023</t>
+          <t>DM-021/2023</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9406400</t>
         </is>
       </c>
       <c r="C1552" t="inlineStr">
@@ -52622,7 +52654,7 @@
       <c r="D1552" t="inlineStr"/>
       <c r="E1552" t="inlineStr">
         <is>
-          <t>2023-08-17 00:00:00</t>
+          <t>2023-11-08 00:00:00</t>
         </is>
       </c>
       <c r="F1552" t="inlineStr">
@@ -52632,19 +52664,19 @@
       </c>
       <c r="G1552" t="inlineStr">
         <is>
-          <t>2301520 000007/2023</t>
+          <t>2301762 000029/2023</t>
         </is>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>DG/AMA-009436677/2024</t>
+          <t>DC-007/2024</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
         <is>
-          <t>9436677</t>
+          <t>9424592</t>
         </is>
       </c>
       <c r="C1553" t="inlineStr">
@@ -52655,7 +52687,7 @@
       <c r="D1553" t="inlineStr"/>
       <c r="E1553" t="inlineStr">
         <is>
-          <t>2024-08-20 00:00:00</t>
+          <t>2024-04-15 00:00:00</t>
         </is>
       </c>
       <c r="F1553" t="inlineStr">
@@ -52665,19 +52697,19 @@
       </c>
       <c r="G1553" t="inlineStr">
         <is>
-          <t>2301617 000002/2024</t>
+          <t>2301520 000024/2023</t>
         </is>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DC-012/2023</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="C1554" t="inlineStr">
@@ -52688,7 +52720,7 @@
       <c r="D1554" t="inlineStr"/>
       <c r="E1554" t="inlineStr">
         <is>
-          <t>2025-08-11 00:00:00</t>
+          <t>2023-08-17 00:00:00</t>
         </is>
       </c>
       <c r="F1554" t="inlineStr">
@@ -52698,19 +52730,19 @@
       </c>
       <c r="G1554" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301520 000007/2023</t>
         </is>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>DM-017/2023</t>
+          <t>DG/AMA-009436677/2024</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
         <is>
-          <t>9400451</t>
+          <t>9436677</t>
         </is>
       </c>
       <c r="C1555" t="inlineStr">
@@ -52721,7 +52753,7 @@
       <c r="D1555" t="inlineStr"/>
       <c r="E1555" t="inlineStr">
         <is>
-          <t>2023-10-27 00:00:00</t>
+          <t>2024-08-20 00:00:00</t>
         </is>
       </c>
       <c r="F1555" t="inlineStr">
@@ -52731,19 +52763,19 @@
       </c>
       <c r="G1555" t="inlineStr">
         <is>
-          <t>2301762 000019/2023</t>
+          <t>2301617 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>DP-008/2023</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
         <is>
-          <t>9386087</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="C1556" t="inlineStr">
@@ -52754,7 +52786,7 @@
       <c r="D1556" t="inlineStr"/>
       <c r="E1556" t="inlineStr">
         <is>
-          <t>2023-04-27 00:00:00</t>
+          <t>2025-08-11 00:00:00</t>
         </is>
       </c>
       <c r="F1556" t="inlineStr">
@@ -52764,19 +52796,19 @@
       </c>
       <c r="G1556" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>DC-019/2023</t>
+          <t>DM-017/2023</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
         <is>
-          <t>9407817</t>
+          <t>9400451</t>
         </is>
       </c>
       <c r="C1557" t="inlineStr">
@@ -52787,7 +52819,7 @@
       <c r="D1557" t="inlineStr"/>
       <c r="E1557" t="inlineStr">
         <is>
-          <t>2023-12-22 00:00:00</t>
+          <t>2023-10-27 00:00:00</t>
         </is>
       </c>
       <c r="F1557" t="inlineStr">
@@ -52797,19 +52829,19 @@
       </c>
       <c r="G1557" t="inlineStr">
         <is>
-          <t>2301520 000021/2023</t>
+          <t>2301762 000019/2023</t>
         </is>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>DM-022/2023</t>
+          <t>DP-008/2023</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
         <is>
-          <t>9408657</t>
+          <t>9386087</t>
         </is>
       </c>
       <c r="C1558" t="inlineStr">
@@ -52820,7 +52852,7 @@
       <c r="D1558" t="inlineStr"/>
       <c r="E1558" t="inlineStr">
         <is>
-          <t>2023-12-22 00:00:00</t>
+          <t>2023-04-27 00:00:00</t>
         </is>
       </c>
       <c r="F1558" t="inlineStr">
@@ -52830,19 +52862,19 @@
       </c>
       <c r="G1558" t="inlineStr">
         <is>
-          <t>2301762 000031/2023</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DC-019/2023</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
         <is>
-          <t>9424377</t>
+          <t>9407817</t>
         </is>
       </c>
       <c r="C1559" t="inlineStr">
@@ -52853,7 +52885,7 @@
       <c r="D1559" t="inlineStr"/>
       <c r="E1559" t="inlineStr">
         <is>
-          <t>2024-04-26 00:00:00</t>
+          <t>2023-12-22 00:00:00</t>
         </is>
       </c>
       <c r="F1559" t="inlineStr">
@@ -52863,19 +52895,19 @@
       </c>
       <c r="G1559" t="inlineStr">
         <is>
-          <t>2301762 000045/2023</t>
+          <t>2301520 000021/2023</t>
         </is>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>DM-010/2023</t>
+          <t>DM-022/2023</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
         <is>
-          <t>9392809</t>
+          <t>9408657</t>
         </is>
       </c>
       <c r="C1560" t="inlineStr">
@@ -52886,7 +52918,7 @@
       <c r="D1560" t="inlineStr"/>
       <c r="E1560" t="inlineStr">
         <is>
-          <t>2023-08-23 00:00:00</t>
+          <t>2023-12-22 00:00:00</t>
         </is>
       </c>
       <c r="F1560" t="inlineStr">
@@ -52896,19 +52928,19 @@
       </c>
       <c r="G1560" t="inlineStr">
         <is>
-          <t>2301762 000009/2023</t>
+          <t>2301762 000031/2023</t>
         </is>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>DM-011/2023</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
         <is>
-          <t>9392828</t>
+          <t>9424377</t>
         </is>
       </c>
       <c r="C1561" t="inlineStr">
@@ -52919,7 +52951,7 @@
       <c r="D1561" t="inlineStr"/>
       <c r="E1561" t="inlineStr">
         <is>
-          <t>2023-08-23 00:00:00</t>
+          <t>2024-04-26 00:00:00</t>
         </is>
       </c>
       <c r="F1561" t="inlineStr">
@@ -52929,19 +52961,19 @@
       </c>
       <c r="G1561" t="inlineStr">
         <is>
-          <t>2301762 000017/2023</t>
+          <t>2301762 000045/2023</t>
         </is>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>DM-009/2023</t>
+          <t>DM-010/2023</t>
         </is>
       </c>
       <c r="B1562" t="inlineStr">
         <is>
-          <t>9392817</t>
+          <t>9392809</t>
         </is>
       </c>
       <c r="C1562" t="inlineStr">
@@ -52962,19 +52994,19 @@
       </c>
       <c r="G1562" t="inlineStr">
         <is>
-          <t>2301762 000018/2023</t>
+          <t>2301762 000009/2023</t>
         </is>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DM-011/2023</t>
         </is>
       </c>
       <c r="B1563" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9392828</t>
         </is>
       </c>
       <c r="C1563" t="inlineStr">
@@ -52985,7 +53017,7 @@
       <c r="D1563" t="inlineStr"/>
       <c r="E1563" t="inlineStr">
         <is>
-          <t>2024-04-25 00:00:00</t>
+          <t>2023-08-23 00:00:00</t>
         </is>
       </c>
       <c r="F1563" t="inlineStr">
@@ -52995,19 +53027,19 @@
       </c>
       <c r="G1563" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000017/2023</t>
         </is>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-009/2023</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9392817</t>
         </is>
       </c>
       <c r="C1564" t="inlineStr">
@@ -53018,7 +53050,7 @@
       <c r="D1564" t="inlineStr"/>
       <c r="E1564" t="inlineStr">
         <is>
-          <t>2026-03-24 00:00:00</t>
+          <t>2023-08-23 00:00:00</t>
         </is>
       </c>
       <c r="F1564" t="inlineStr">
@@ -53028,19 +53060,19 @@
       </c>
       <c r="G1564" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000018/2023</t>
         </is>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C1565" t="inlineStr">
@@ -53051,7 +53083,7 @@
       <c r="D1565" t="inlineStr"/>
       <c r="E1565" t="inlineStr">
         <is>
-          <t>2026-05-14 00:00:00</t>
+          <t>2024-04-25 00:00:00</t>
         </is>
       </c>
       <c r="F1565" t="inlineStr">
@@ -53061,19 +53093,19 @@
       </c>
       <c r="G1565" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C1566" t="inlineStr">
@@ -53084,7 +53116,7 @@
       <c r="D1566" t="inlineStr"/>
       <c r="E1566" t="inlineStr">
         <is>
-          <t>2026-05-14 00:00:00</t>
+          <t>2026-03-24 00:00:00</t>
         </is>
       </c>
       <c r="F1566" t="inlineStr">
@@ -53094,19 +53126,19 @@
       </c>
       <c r="G1566" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C1567" t="inlineStr">
@@ -53117,7 +53149,7 @@
       <c r="D1567" t="inlineStr"/>
       <c r="E1567" t="inlineStr">
         <is>
-          <t>2026-06-12 00:00:00</t>
+          <t>2026-05-14 00:00:00</t>
         </is>
       </c>
       <c r="F1567" t="inlineStr">
@@ -53127,19 +53159,19 @@
       </c>
       <c r="G1567" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C1568" t="inlineStr">
@@ -53150,7 +53182,7 @@
       <c r="D1568" t="inlineStr"/>
       <c r="E1568" t="inlineStr">
         <is>
-          <t>2026-03-20 00:00:00</t>
+          <t>2026-06-12 00:00:00</t>
         </is>
       </c>
       <c r="F1568" t="inlineStr">
@@ -53160,19 +53192,19 @@
       </c>
       <c r="G1568" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C1569" t="inlineStr">
@@ -53183,7 +53215,7 @@
       <c r="D1569" t="inlineStr"/>
       <c r="E1569" t="inlineStr">
         <is>
-          <t>2026-04-16 00:00:00</t>
+          <t>2026-03-20 00:00:00</t>
         </is>
       </c>
       <c r="F1569" t="inlineStr">
@@ -53193,17 +53225,21 @@
       </c>
       <c r="G1569" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B1570" t="inlineStr"/>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
       <c r="C1570" t="inlineStr">
         <is>
           <t>A Iniciar</t>
@@ -53212,7 +53248,7 @@
       <c r="D1570" t="inlineStr"/>
       <c r="E1570" t="inlineStr">
         <is>
-          <t>2026-06-18 00:00:00</t>
+          <t>2026-04-16 00:00:00</t>
         </is>
       </c>
       <c r="F1570" t="inlineStr">
@@ -53220,17 +53256,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G1570" t="inlineStr"/>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C1571" t="inlineStr">
@@ -53241,7 +53281,7 @@
       <c r="D1571" t="inlineStr"/>
       <c r="E1571" t="inlineStr">
         <is>
-          <t>2026-04-23 00:00:00</t>
+          <t>2026-06-18 00:00:00</t>
         </is>
       </c>
       <c r="F1571" t="inlineStr">
@@ -53251,19 +53291,19 @@
       </c>
       <c r="G1571" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C1572" t="inlineStr">
@@ -53274,7 +53314,7 @@
       <c r="D1572" t="inlineStr"/>
       <c r="E1572" t="inlineStr">
         <is>
-          <t>2026-03-31 00:00:00</t>
+          <t>2026-04-23 00:00:00</t>
         </is>
       </c>
       <c r="F1572" t="inlineStr">
@@ -53284,19 +53324,19 @@
       </c>
       <c r="G1572" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C1573" t="inlineStr">
@@ -53307,7 +53347,7 @@
       <c r="D1573" t="inlineStr"/>
       <c r="E1573" t="inlineStr">
         <is>
-          <t>2026-05-06 00:00:00</t>
+          <t>2026-03-31 00:00:00</t>
         </is>
       </c>
       <c r="F1573" t="inlineStr">
@@ -53317,19 +53357,19 @@
       </c>
       <c r="G1573" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C1574" t="inlineStr">
@@ -53340,7 +53380,7 @@
       <c r="D1574" t="inlineStr"/>
       <c r="E1574" t="inlineStr">
         <is>
-          <t>2026-05-07 00:00:00</t>
+          <t>2026-05-06 00:00:00</t>
         </is>
       </c>
       <c r="F1574" t="inlineStr">
@@ -53350,7 +53390,7 @@
       </c>
       <c r="G1574" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
